--- a/content/tz-druzhba-na-kitayskom-ieroglif.xlsx
+++ b/content/tz-druzhba-na-kitayskom-ieroglif.xlsx
@@ -649,7 +649,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Иероглиф «дружба»: как 友 восходит к двум рукам и почему входит в слово 朋友</t>
+          <t>Дружба по-китайски: как устроен иероглиф 友 и как его запомнить</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
@@ -664,7 +664,7 @@
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>Что за знак и как он устроен · Две руки: откуда взялся знак · Как писать: четыре черты по порядку · Та же рука ещё в двух знаках · Из личного опыта · Почему «друг» — это 朋友 · Слова с 友 · Не перепутайте: 友, 有 и 反 · Дружба по-китайски · Как запомнить знак · FAQ</t>
+          <t>Что за знак и как он устроен · Две руки: откуда взялся знак · Как писать: четыре черты по порядку · Та же рука ещё в двух знаках · Из личного опыта · Почему «друг» — это 朋友 · Слова с 友 · Не перепутайте: 友, 有 и 反 · Кого китайцы называют 朋友 · Как запомнить знак · FAQ</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
@@ -2260,7 +2260,7 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>Иероглиф «дружба»: как 友 восходит к двум рукам и почему входит в слово 朋友</t>
+          <t>Дружба по-китайски: как устроен иероглиф 友 и как его запомнить</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
@@ -2304,7 +2304,7 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>Иероглиф «дружба»: как 友 восходит к двум рукам и почему входит в слово 朋友</t>
+          <t>Дружба по-китайски: как устроен иероглиф 友 и как его запомнить</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
